--- a/plantillas/38.xlsx
+++ b/plantillas/38.xlsx
@@ -24,7 +24,7 @@
     <definedName name="MARCA_10">Listas!$M$2:$M$2</definedName>
     <definedName name="MARCA_11">Listas!$N$2:$N$6</definedName>
     <definedName name="MARCA_12">Listas!$O$2:$O$5</definedName>
-    <definedName name="MARCA_13">Listas!$P$2:$P$13</definedName>
+    <definedName name="MARCA_13">Listas!$P$2:$P$12</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$4</definedName>
     <definedName name="MARCA_16">Listas!$S$2:$S$2</definedName>
@@ -640,11 +640,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B3,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B3,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B3,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B3,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -664,11 +664,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B4,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B4,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B4,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B4,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -688,11 +688,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B5,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B5,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B5,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B5,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -712,11 +712,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B6,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B6,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B6,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B6,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -731,11 +731,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B7,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B7,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B7,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B7,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -750,11 +750,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B8,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B8,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B8,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B8,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -769,11 +769,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B9,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B9,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B9,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B9,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -788,11 +788,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B10,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B10,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B10,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B10,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -807,11 +807,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B11,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B11,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B11,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B11,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -826,11 +826,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B12,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B12,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B12,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B12,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -845,11 +845,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B13,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B13,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B13,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B13,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -864,11 +864,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B14,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B14,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B14,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B14,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -883,11 +883,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B15,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B15,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B15,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B15,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -902,11 +902,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B16,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B16,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B16,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B16,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -921,11 +921,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B17,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B17,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B17,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B17,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -940,11 +940,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B18,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B18,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B18,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B18,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -959,11 +959,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B19,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B19,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B19,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B19,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -978,11 +978,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B20,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B20,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B20,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B20,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -997,11 +997,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B21,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B21,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B21,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B21,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1016,11 +1016,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B22,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B22,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B22,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B22,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1035,11 +1035,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B23,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B23,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B23,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B23,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1054,11 +1054,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B24,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B24,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B24,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B24,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1073,11 +1073,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B25,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B25,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B25,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B25,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1092,11 +1092,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B26,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B26,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B26,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B26,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1111,11 +1111,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B27,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B27,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B27,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B27,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1130,11 +1130,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B28,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B28,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B28,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B28,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1149,11 +1149,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B29,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B29,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B29,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B29,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1168,11 +1168,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B30,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B30,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B30,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B30,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1187,11 +1187,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B31,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B31,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B31,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B31,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1206,11 +1206,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B32,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B32,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B32,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B32,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1225,11 +1225,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B33,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B33,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B33,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B33,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1244,11 +1244,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B34,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B34,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B34,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B34,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1263,11 +1263,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B35,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B35,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B35,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B35,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1282,11 +1282,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B36,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B36,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B36,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B36,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1301,11 +1301,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B37,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B37,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B37,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B37,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1320,11 +1320,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B38,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B38,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B38,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B38,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1339,11 +1339,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B39,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B39,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B39,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B39,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1358,11 +1358,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B40,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B40,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B40,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B40,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1377,11 +1377,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B41,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B41,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B41,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B41,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1396,11 +1396,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B42,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B42,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B42,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B42,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1415,11 +1415,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B43,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B43,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B43,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B43,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1434,11 +1434,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B44,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B44,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B44,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B44,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1453,11 +1453,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B45,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B45,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B45,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B45,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1472,11 +1472,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B46,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B46,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B46,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B46,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1491,11 +1491,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B47,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B47,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B47,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B47,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1510,11 +1510,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B48,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B48,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B48,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B48,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1529,11 +1529,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B49,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B49,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B49,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B49,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1548,11 +1548,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B50,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B50,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B50,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B50,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1567,11 +1567,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B51,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B51,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B51,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B51,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1586,11 +1586,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B52,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B52,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B52,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B52,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1605,11 +1605,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B53,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B53,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B53,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B53,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1624,11 +1624,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B54,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B54,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B54,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B54,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1643,11 +1643,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B55,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B55,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B55,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B55,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1662,11 +1662,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B56,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B56,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B56,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B56,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1681,11 +1681,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B57,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B57,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B57,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B57,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1700,11 +1700,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B58,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B58,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B58,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B58,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1719,11 +1719,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B59,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B59,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B59,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B59,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1738,11 +1738,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B60,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B60,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B60,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B60,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1757,11 +1757,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B61,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B61,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B61,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B61,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1776,11 +1776,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B62,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B62,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B62,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B62,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1795,11 +1795,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B63,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B63,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B63,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B63,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1814,11 +1814,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B64,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B64,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B64,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B64,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1833,11 +1833,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B65,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B65,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B65,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B65,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1852,11 +1852,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B66,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B66,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B66,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B66,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1871,11 +1871,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B67,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B67,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B67,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B67,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1890,11 +1890,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B68,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B68,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B68,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B68,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1909,11 +1909,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B69,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B69,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B69,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B69,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1928,11 +1928,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B70,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B70,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B70,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B70,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1947,11 +1947,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B71,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B71,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B71,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B71,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1966,11 +1966,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B72,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B72,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B72,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B72,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1985,11 +1985,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B73,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B73,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B73,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B73,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2004,11 +2004,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B74,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B74,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B74,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B74,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2023,11 +2023,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B75,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B75,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B75,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B75,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2042,11 +2042,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B76,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B76,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B76,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B76,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2061,11 +2061,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B77,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B77,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B77,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B77,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2080,11 +2080,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B78,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B78,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B78,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B78,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2099,11 +2099,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B79,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B79,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B79,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B79,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2118,11 +2118,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B80,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B80,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B80,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B80,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2137,11 +2137,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B81,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B81,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B81,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B81,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2156,11 +2156,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B82,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B82,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B82,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B82,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2175,11 +2175,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B83,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B83,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B83,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B83,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2194,11 +2194,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B84,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B84,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B84,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B84,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2213,11 +2213,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B85,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B85,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B85,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B85,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2232,11 +2232,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B86,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B86,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B86,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B86,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2251,11 +2251,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B87,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B87,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B87,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B87,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2270,11 +2270,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B88,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B88,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B88,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B88,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2289,11 +2289,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B89,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B89,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B89,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B89,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2308,11 +2308,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B90,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B90,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B90,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B90,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2327,11 +2327,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B91,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B91,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B91,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B91,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2346,11 +2346,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B92,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B92,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B92,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B92,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2365,11 +2365,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B93,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B93,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B93,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B93,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2384,11 +2384,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B94,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B94,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B94,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B94,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2403,11 +2403,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B95,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B95,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B95,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B95,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2422,11 +2422,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B96,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B96,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B96,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B96,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2441,11 +2441,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B97,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B97,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B97,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B97,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2460,11 +2460,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B98,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B98,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B98,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B98,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2479,11 +2479,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B99,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B99,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B99,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B99,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2498,11 +2498,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B100,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B100,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B100,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B100,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2517,11 +2517,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B101,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B101,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B101,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B101,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2536,11 +2536,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B102,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B102,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B102,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B102,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2555,11 +2555,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B103,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B103,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B103,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B103,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2574,11 +2574,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B104,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B104,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B104,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B104,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2593,11 +2593,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B105,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B105,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B105,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B105,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2612,11 +2612,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B106,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B106,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B106,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B106,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2631,11 +2631,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B107,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B107,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B107,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B107,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2650,11 +2650,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B108,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B108,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B108,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B108,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2669,11 +2669,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B109,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B109,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B109,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B109,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2688,11 +2688,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B110,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B110,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B110,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B110,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2707,11 +2707,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B111,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B111,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B111,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B111,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2726,11 +2726,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B112,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B112,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B112,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B112,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2745,11 +2745,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B113,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B113,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B113,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B113,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2764,11 +2764,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B114,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B114,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B114,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B114,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2783,11 +2783,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B115,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B115,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B115,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B115,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2802,11 +2802,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B116,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B116,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B116,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B116,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2821,11 +2821,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B117,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B117,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B117,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B117,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2840,11 +2840,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B118,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B118,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B118,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B118,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2859,11 +2859,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B119,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B119,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B119,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B119,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2878,11 +2878,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B120,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B120,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B120,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B120,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2897,11 +2897,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B121,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B121,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B121,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B121,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2916,11 +2916,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B122,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B122,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B122,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B122,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2935,11 +2935,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B123,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B123,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B123,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B123,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2954,11 +2954,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B124,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B124,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B124,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B124,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2973,11 +2973,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B125,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B125,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B125,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B125,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2992,11 +2992,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B126,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B126,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B126,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B126,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3011,11 +3011,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B127,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B127,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B127,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B127,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3030,11 +3030,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B128,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B128,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B128,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B128,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3049,11 +3049,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B129,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B129,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B129,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B129,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3068,11 +3068,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B130,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B130,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B130,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B130,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3087,11 +3087,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B131,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B131,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B131,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B131,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3106,11 +3106,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B132,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B132,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B132,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B132,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3125,11 +3125,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B133,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B133,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B133,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B133,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3144,11 +3144,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B134,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B134,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B134,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B134,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3163,11 +3163,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B135,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B135,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B135,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B135,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3182,11 +3182,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B136,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B136,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B136,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B136,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3201,11 +3201,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B137,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B137,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B137,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B137,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3220,11 +3220,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B138,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B138,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B138,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B138,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3239,11 +3239,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B139,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B139,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B139,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B139,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3258,11 +3258,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B140,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B140,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B140,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B140,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3277,11 +3277,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B141,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B141,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B141,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B141,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3296,11 +3296,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B142,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B142,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B142,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B142,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3315,11 +3315,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B143,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B143,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B143,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B143,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3334,11 +3334,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B144,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B144,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B144,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B144,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3353,11 +3353,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B145,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B145,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B145,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B145,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3372,11 +3372,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B146,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B146,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B146,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B146,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3391,11 +3391,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B147,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B147,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B147,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B147,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3410,11 +3410,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B148,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B148,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B148,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B148,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3429,11 +3429,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B149,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B149,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B149,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B149,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3448,11 +3448,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B150,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B150,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B150,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B150,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3467,11 +3467,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B151,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B151,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B151,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B151,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3486,11 +3486,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B152,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B152,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B152,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B152,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3505,11 +3505,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B153,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B153,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B153,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B153,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3524,11 +3524,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B154,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B154,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B154,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B154,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3543,11 +3543,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B155,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B155,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B155,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B155,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3562,11 +3562,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B156,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B156,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B156,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B156,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3581,11 +3581,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B157,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B157,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B157,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B157,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3600,11 +3600,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B158,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B158,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B158,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B158,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3619,11 +3619,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B159,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B159,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B159,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B159,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3638,11 +3638,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B160,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B160,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B160,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B160,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3657,11 +3657,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B161,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B161,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B161,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B161,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3676,11 +3676,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B162,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B162,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B162,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B162,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3695,11 +3695,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B163,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B163,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B163,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B163,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3714,11 +3714,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B164,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B164,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B164,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B164,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3733,11 +3733,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B165,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B165,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B165,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B165,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3752,11 +3752,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B166,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B166,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B166,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B166,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3771,11 +3771,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B167,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B167,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B167,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B167,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3790,11 +3790,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B168,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B168,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B168,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B168,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3809,11 +3809,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B169,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B169,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B169,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B169,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3828,11 +3828,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B170,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B170,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B170,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B170,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3847,11 +3847,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B171,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B171,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B171,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B171,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3866,11 +3866,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B172,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B172,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B172,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B172,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3885,11 +3885,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B173,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B173,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B173,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B173,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3904,11 +3904,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B174,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B174,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B174,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B174,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3923,11 +3923,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B175,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B175,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B175,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B175,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3942,11 +3942,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B176,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B176,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B176,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B176,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3961,11 +3961,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B177,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B177,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B177,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B177,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3980,11 +3980,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B178,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B178,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B178,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B178,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3999,11 +3999,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B179,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B179,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B179,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B179,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4018,11 +4018,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B180,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B180,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B180,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B180,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4037,11 +4037,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B181,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B181,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B181,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B181,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4056,11 +4056,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B182,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B182,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B182,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B182,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4075,11 +4075,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B183,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B183,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B183,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B183,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4094,11 +4094,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B184,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B184,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B184,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B184,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4113,11 +4113,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B185,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B185,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B185,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B185,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4132,11 +4132,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B186,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B186,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B186,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B186,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4151,11 +4151,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B187,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B187,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B187,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B187,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4170,11 +4170,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B188,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B188,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B188,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B188,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4189,11 +4189,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B189,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B189,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B189,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B189,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4208,11 +4208,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B190,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B190,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B190,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B190,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4227,11 +4227,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B191,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B191,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B191,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B191,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4246,11 +4246,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B192,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B192,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B192,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B192,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4265,11 +4265,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B193,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B193,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B193,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B193,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4284,11 +4284,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B194,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B194,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B194,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B194,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4303,11 +4303,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B195,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B195,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B195,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B195,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4322,11 +4322,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B196,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B196,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B196,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B196,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4341,11 +4341,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B197,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B197,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B197,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B197,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4360,11 +4360,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B198,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B198,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B198,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B198,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4379,11 +4379,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B199,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B199,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B199,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B199,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4398,11 +4398,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B200,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B200,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B200,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B200,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4417,11 +4417,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B201,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B201,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B201,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B201,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4436,11 +4436,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B202,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B202,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B202,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B202,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4455,11 +4455,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B203,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B203,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B203,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B203,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4474,11 +4474,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B204,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B204,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B204,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B204,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4493,11 +4493,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B205,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B205,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B205,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B205,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4512,11 +4512,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B206,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B206,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B206,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B206,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4531,11 +4531,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B207,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B207,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B207,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B207,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4550,11 +4550,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B208,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B208,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B208,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B208,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4569,11 +4569,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B209,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B209,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B209,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B209,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4588,11 +4588,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B210,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B210,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B210,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B210,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4607,11 +4607,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B211,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B211,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B211,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B211,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4626,11 +4626,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B212,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B212,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B212,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B212,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4645,11 +4645,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B213,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B213,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B213,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B213,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4664,11 +4664,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B214,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B214,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B214,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B214,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4683,11 +4683,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B215,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B215,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B215,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B215,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4702,11 +4702,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B216,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B216,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B216,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B216,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4721,11 +4721,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B217,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B217,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B217,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B217,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4740,11 +4740,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B218,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B218,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B218,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B218,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4759,11 +4759,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B219,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B219,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B219,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B219,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4778,11 +4778,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B220,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B220,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B220,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B220,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4797,11 +4797,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B221,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B221,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B221,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B221,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4816,11 +4816,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B222,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B222,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B222,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B222,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4835,11 +4835,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B223,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B223,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B223,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B223,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4854,11 +4854,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B224,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B224,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B224,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B224,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4873,11 +4873,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B225,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B225,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B225,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B225,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4892,11 +4892,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B226,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B226,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B226,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B226,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4911,11 +4911,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B227,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B227,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B227,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B227,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4930,11 +4930,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B228,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B228,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B228,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B228,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4949,11 +4949,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B229,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B229,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B229,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B229,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4968,11 +4968,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B230,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B230,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B230,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B230,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4987,11 +4987,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B231,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B231,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B231,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B231,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5006,11 +5006,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B232,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B232,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B232,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B232,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5025,11 +5025,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B233,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B233,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B233,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B233,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5044,11 +5044,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B234,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B234,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B234,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B234,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5063,11 +5063,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B235,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B235,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B235,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B235,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5082,11 +5082,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B236,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B236,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B236,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B236,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5101,11 +5101,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B237,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B237,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B237,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B237,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5120,11 +5120,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B238,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B238,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B238,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B238,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5139,11 +5139,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B239,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B239,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B239,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B239,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5158,11 +5158,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B240,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B240,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B240,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B240,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5177,11 +5177,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B241,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B241,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B241,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B241,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5196,11 +5196,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B242,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B242,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B242,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B242,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5215,11 +5215,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B243,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B243,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B243,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B243,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5234,11 +5234,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B244,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B244,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B244,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B244,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5253,11 +5253,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B245,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B245,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B245,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B245,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5272,11 +5272,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B246,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B246,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B246,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B246,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5291,11 +5291,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B247,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B247,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B247,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B247,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5310,11 +5310,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B248,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B248,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B248,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B248,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5329,11 +5329,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B249,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B249,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B249,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B249,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5348,11 +5348,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B250,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B250,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B250,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B250,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5367,11 +5367,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B251,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B251,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B251,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B251,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5386,11 +5386,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B252,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B252,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B252,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B252,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5405,11 +5405,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B253,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B253,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B253,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B253,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5424,11 +5424,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B254,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B254,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B254,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B254,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5443,11 +5443,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B255,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B255,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B255,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B255,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5462,11 +5462,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B256,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B256,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B256,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B256,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5481,11 +5481,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B257,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B257,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B257,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B257,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5500,11 +5500,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B258,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B258,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B258,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B258,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5519,11 +5519,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B259,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B259,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B259,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B259,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5538,11 +5538,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B260,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B260,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B260,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B260,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5557,11 +5557,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B261,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B261,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B261,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B261,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5576,11 +5576,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B262,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B262,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B262,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B262,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5595,11 +5595,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B263,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B263,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B263,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B263,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5614,11 +5614,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B264,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B264,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B264,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B264,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5633,11 +5633,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B265,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B265,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B265,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B265,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5652,11 +5652,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B266,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B266,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B266,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B266,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5671,11 +5671,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B267,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B267,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B267,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B267,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5690,11 +5690,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B268,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B268,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B268,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B268,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5709,11 +5709,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B269,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B269,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B269,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B269,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5728,11 +5728,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B270,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B270,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B270,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B270,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5747,11 +5747,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B271,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B271,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B271,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B271,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5766,11 +5766,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B272,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B272,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B272,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B272,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5785,11 +5785,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B273,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B273,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B273,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B273,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5804,11 +5804,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B274,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B274,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B274,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B274,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5823,11 +5823,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B275,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B275,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B275,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B275,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5842,11 +5842,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B276,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B276,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B276,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B276,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5861,11 +5861,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B277,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B277,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B277,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B277,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5880,11 +5880,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B278,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B278,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B278,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B278,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5899,11 +5899,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B279,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B279,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B279,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B279,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5918,11 +5918,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B280,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B280,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B280,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B280,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5937,11 +5937,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B281,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B281,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B281,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B281,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5956,11 +5956,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B282,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B282,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B282,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B282,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5975,11 +5975,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B283,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B283,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B283,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B283,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5994,11 +5994,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B284,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B284,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B284,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B284,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6013,11 +6013,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B285,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B285,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B285,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B285,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6032,11 +6032,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B286,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B286,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B286,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B286,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6051,11 +6051,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B287,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B287,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B287,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B287,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6070,11 +6070,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B288,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B288,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B288,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B288,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6089,11 +6089,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B289,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B289,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B289,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B289,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6108,11 +6108,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B290,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B290,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B290,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B290,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6127,11 +6127,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B291,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B291,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B291,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B291,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6146,11 +6146,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B292,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B292,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B292,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B292,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6165,11 +6165,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B293,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B293,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B293,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B293,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6184,11 +6184,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B294,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B294,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B294,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B294,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6203,11 +6203,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B295,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B295,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B295,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B295,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6222,11 +6222,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B296,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B296,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B296,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B296,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6241,11 +6241,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B297,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B297,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B297,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B297,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6260,11 +6260,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B298,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B298,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B298,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B298,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6279,11 +6279,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B299,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B299,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B299,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B299,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6298,11 +6298,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B300,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B300,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B300,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B300,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6317,11 +6317,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B301,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B301,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B301,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B301,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6336,11 +6336,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B302,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B302,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B302,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B302,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6355,11 +6355,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B303,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B303,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B303,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B303,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6374,11 +6374,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B304,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B304,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B304,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B304,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6393,11 +6393,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B305,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B305,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B305,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B305,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6412,11 +6412,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B306,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B306,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B306,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B306,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6431,11 +6431,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B307,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B307,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B307,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B307,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6450,11 +6450,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B308,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B308,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B308,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B308,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6469,11 +6469,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B309,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B309,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B309,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B309,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6488,11 +6488,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B310,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B310,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B310,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B310,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6507,11 +6507,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B311,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B311,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B311,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B311,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6526,11 +6526,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B312,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B312,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B312,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B312,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6545,11 +6545,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B313,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B313,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B313,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B313,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6564,11 +6564,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B314,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B314,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B314,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B314,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6583,11 +6583,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B315,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B315,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B315,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B315,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6602,11 +6602,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B316,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B316,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B316,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B316,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6621,11 +6621,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B317,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B317,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B317,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B317,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6640,11 +6640,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B318,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B318,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B318,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B318,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6659,11 +6659,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B319,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B319,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B319,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B319,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6678,11 +6678,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B320,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B320,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B320,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B320,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6697,11 +6697,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B321,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B321,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B321,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B321,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6716,11 +6716,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B322,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B322,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B322,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B322,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6735,11 +6735,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B323,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B323,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B323,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B323,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6754,11 +6754,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B324,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B324,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B324,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B324,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6773,11 +6773,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B325,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B325,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B325,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B325,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6792,11 +6792,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B326,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B326,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B326,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B326,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6811,11 +6811,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B327,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B327,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B327,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B327,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6830,11 +6830,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B328,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B328,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B328,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B328,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6849,11 +6849,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B329,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B329,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B329,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B329,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6868,11 +6868,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B330,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B330,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B330,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B330,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6887,11 +6887,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B331,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B331,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B331,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B331,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6906,11 +6906,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B332,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B332,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B332,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B332,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6925,11 +6925,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B333,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B333,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B333,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B333,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6944,11 +6944,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B334,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B334,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B334,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B334,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6963,11 +6963,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B335,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B335,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B335,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B335,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6982,11 +6982,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B336,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B336,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B336,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B336,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7001,11 +7001,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B337,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B337,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B337,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B337,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7020,11 +7020,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B338,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B338,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B338,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B338,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7039,11 +7039,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B339,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B339,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B339,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B339,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7058,11 +7058,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B340,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B340,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B340,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B340,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7077,11 +7077,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B341,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B341,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B341,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B341,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7096,11 +7096,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B342,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B342,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B342,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B342,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7115,11 +7115,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B343,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B343,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B343,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B343,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7134,11 +7134,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B344,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B344,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B344,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B344,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7153,11 +7153,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B345,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B345,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B345,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B345,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7172,11 +7172,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B346,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B346,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B346,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B346,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7191,11 +7191,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B347,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B347,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B347,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B347,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7210,11 +7210,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B348,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B348,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B348,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B348,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7229,11 +7229,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B349,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B349,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B349,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B349,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7248,11 +7248,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B350,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B350,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B350,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B350,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7267,11 +7267,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B351,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B351,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B351,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B351,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7286,11 +7286,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B352,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B352,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B352,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B352,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7305,11 +7305,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B353,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B353,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B353,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B353,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7324,11 +7324,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B354,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B354,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B354,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B354,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7343,11 +7343,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B355,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B355,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B355,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B355,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7362,11 +7362,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B356,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B356,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B356,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B356,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7381,11 +7381,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B357,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B357,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B357,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B357,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7400,11 +7400,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B358,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B358,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B358,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B358,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7419,11 +7419,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B359,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B359,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B359,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B359,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7438,11 +7438,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B360,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B360,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B360,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B360,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7457,11 +7457,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B361,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B361,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B361,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B361,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7476,11 +7476,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B362,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B362,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B362,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B362,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7495,11 +7495,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B363,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B363,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B363,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B363,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7514,11 +7514,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B364,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B364,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B364,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B364,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7533,11 +7533,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B365,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B365,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B365,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B365,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7552,11 +7552,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B366,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B366,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B366,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B366,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7571,11 +7571,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B367,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B367,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B367,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B367,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7590,11 +7590,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B368,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B368,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B368,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B368,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7609,11 +7609,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B369,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B369,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B369,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B369,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7628,11 +7628,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B370,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B370,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B370,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B370,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7647,11 +7647,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B371,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B371,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B371,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B371,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7666,11 +7666,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B372,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B372,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B372,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B372,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7685,11 +7685,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B373,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B373,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B373,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B373,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7704,11 +7704,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B374,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B374,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B374,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B374,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7723,11 +7723,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B375,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B375,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B375,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B375,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7742,11 +7742,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B376,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B376,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B376,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B376,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7761,11 +7761,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B377,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B377,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B377,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B377,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7780,11 +7780,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B378,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B378,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B378,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B378,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7799,11 +7799,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B379,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B379,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B379,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B379,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7818,11 +7818,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B380,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B380,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B380,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B380,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7837,11 +7837,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B381,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B381,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B381,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B381,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7856,11 +7856,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B382,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B382,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B382,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B382,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7875,11 +7875,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B383,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B383,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B383,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B383,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7894,11 +7894,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B384,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B384,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B384,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B384,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7913,11 +7913,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B385,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B385,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B385,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B385,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7932,11 +7932,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B386,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B386,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B386,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B386,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7951,11 +7951,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B387,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B387,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B387,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B387,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7970,11 +7970,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B388,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B388,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B388,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B388,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7989,11 +7989,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B389,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B389,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B389,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B389,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8008,11 +8008,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B390,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B390,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B390,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B390,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8027,11 +8027,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B391,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B391,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B391,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B391,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8046,11 +8046,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B392,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B392,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B392,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B392,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8065,11 +8065,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B393,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B393,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B393,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B393,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8084,11 +8084,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B394,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B394,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B394,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B394,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8103,11 +8103,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B395,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B395,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B395,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B395,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8122,11 +8122,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B396,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B396,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B396,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B396,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8141,11 +8141,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B397,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B397,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B397,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B397,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8160,11 +8160,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B398,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B398,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B398,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B398,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8179,11 +8179,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B399,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B399,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B399,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B399,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8198,11 +8198,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B400,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B400,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B400,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B400,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8217,11 +8217,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B401,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B401,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B401,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B401,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8236,11 +8236,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$77,MATCH(B402,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B402,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$77,MATCH(B402,Productos!$A$2:$A$77,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B402,Productos!$A$2:$A$76,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
     </row>
@@ -8943,11 +8943,6 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>MARCA_12</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9599,7 +9594,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9659,7 +9654,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9699,7 +9694,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9739,7 +9734,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9770,16 +9765,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -9790,16 +9785,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9810,16 +9805,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9830,16 +9825,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9850,16 +9845,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9870,16 +9865,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -9890,16 +9885,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9910,16 +9905,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9930,16 +9925,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90410970000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -9950,16 +9945,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -9970,16 +9965,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -9990,36 +9985,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>OLA COBAYOS 800GRS. · 90405610000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90405610000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OLA COBAYOS 800GRS. · 90405610000</t>
+          <t>OLA CONEJOS 800GRS · 90405620000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90405610000</t>
+          <t>90405620000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10030,16 +10025,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OLA CONEJOS 800GRS · 90405620000</t>
+          <t>OLA HAMSTERS 800GRS · 90405600000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90405620000</t>
+          <t>90405600000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10050,36 +10045,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OLA HAMSTERS 800GRS · 90405600000</t>
+          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90405600000</t>
+          <t>93509400000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
+          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93509400000</t>
+          <t>93509410000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10090,16 +10085,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
+          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93509410000</t>
+          <t>93512280000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10110,52 +10105,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93512280000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D WS POLLO Y ARROZ INTEGRAL 30L · 93500000230</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93500000230</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUNSHINE MILLS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D WS POLLO Y ARROZ INTEGRAL 30L · 93500000230</t>
+          <t>D SK ALIM LATA POLLO 400GR · 93511650000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93500000230</t>
+          <t>93511650000</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -10163,23 +10158,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SUNSHINE MILLS</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA POLLO 400GR · 93511650000</t>
+          <t>D SK ALIM LATA POLLO/RES/TOCINO 400GR · 93511660000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93511650000</t>
+          <t>93511660000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10190,16 +10185,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA POLLO/RES/TOCINO 400GR · 93511660000</t>
+          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93511660000</t>
+          <t>93511640000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10210,16 +10205,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
+          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>93511640000</t>
+          <t>93511680000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10230,16 +10225,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>93511680000</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10250,16 +10245,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10270,16 +10265,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ADULTOS 4KG · 93500000343</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93500000343</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10290,16 +10285,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 4KG · 93500000343</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>93500000343</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10310,16 +10305,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10330,36 +10325,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>D SUPRA ALIM LATA TROZOS D CARNE 14OZ · 93509270000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93509270000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D SUPRA ALIM LATA TROZOS D CARNE 14OZ · 93509270000</t>
+          <t>D SUPRA ALIM LATA TROZOS D POLLO 14OZ · 93509280000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>93509270000</t>
+          <t>93509280000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10370,16 +10365,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D SUPRA ALIM LATA TROZOS D POLLO 14OZ · 93509280000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>93509280000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10390,16 +10385,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10410,16 +10405,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10430,16 +10425,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10450,16 +10445,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10470,16 +10465,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508950000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10490,16 +10485,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93508950000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10510,56 +10505,56 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90409060000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90409060000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10570,16 +10565,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90409050000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10590,74 +10585,54 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>90409070000</t>
+          <t>93503060000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>93503060000</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>4</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
           <t>ZOO MED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MELO &amp; CIA. | LA VILLA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MELO &amp; CIA. | LA VILLA</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>19.10.2026</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/38.xlsx
+++ b/plantillas/38.xlsx
@@ -22,7 +22,7 @@
     <definedName name="MARCA_8">Listas!$K$2:$K$2</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$4</definedName>
     <definedName name="MARCA_10">Listas!$M$2:$M$2</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$6</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$5</definedName>
     <definedName name="MARCA_12">Listas!$O$2:$O$5</definedName>
     <definedName name="MARCA_13">Listas!$P$2:$P$12</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
@@ -640,11 +640,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B3,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B3,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B3,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B3,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -664,11 +664,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B4,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B4,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B4,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B4,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -688,11 +688,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B5,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B5,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B5,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B5,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -712,11 +712,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B6,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B6,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B6,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B6,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -731,11 +731,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B7,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B7,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B7,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B7,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -750,11 +750,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B8,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B8,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B8,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B8,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -769,11 +769,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B9,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B9,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B9,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B9,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -788,11 +788,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B10,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B10,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B10,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B10,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -807,11 +807,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B11,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B11,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B11,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B11,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -826,11 +826,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B12,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B12,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B12,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B12,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -845,11 +845,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B13,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B13,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B13,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B13,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -864,11 +864,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B14,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B14,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B14,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B14,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -883,11 +883,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B15,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B15,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B15,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B15,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -902,11 +902,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B16,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B16,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B16,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B16,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -921,11 +921,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B17,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B17,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B17,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B17,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -940,11 +940,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B18,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B18,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B18,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B18,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -959,11 +959,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B19,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B19,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B19,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B19,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -978,11 +978,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B20,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B20,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B20,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B20,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -997,11 +997,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B21,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B21,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B21,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B21,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1016,11 +1016,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B22,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B22,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B22,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B22,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1035,11 +1035,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B23,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B23,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B23,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B23,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1054,11 +1054,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B24,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B24,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B24,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B24,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1073,11 +1073,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B25,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B25,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B25,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B25,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1092,11 +1092,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B26,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B26,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B26,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B26,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1111,11 +1111,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B27,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B27,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B27,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B27,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1130,11 +1130,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B28,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B28,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B28,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B28,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1149,11 +1149,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B29,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B29,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B29,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B29,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1168,11 +1168,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B30,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B30,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B30,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B30,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1187,11 +1187,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B31,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B31,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B31,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B31,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1206,11 +1206,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B32,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B32,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B32,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B32,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1225,11 +1225,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B33,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B33,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B33,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B33,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1244,11 +1244,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B34,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B34,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B34,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B34,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1263,11 +1263,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B35,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B35,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B35,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B35,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1282,11 +1282,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B36,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B36,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B36,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B36,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1301,11 +1301,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B37,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B37,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B37,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B37,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1320,11 +1320,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B38,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B38,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B38,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B38,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1339,11 +1339,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B39,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B39,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B39,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B39,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1358,11 +1358,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B40,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B40,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B40,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B40,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1377,11 +1377,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B41,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B41,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B41,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B41,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1396,11 +1396,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B42,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B42,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B42,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B42,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1415,11 +1415,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B43,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B43,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B43,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B43,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1434,11 +1434,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B44,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B44,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B44,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B44,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1453,11 +1453,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B45,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B45,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B45,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B45,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1472,11 +1472,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B46,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B46,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B46,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B46,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1491,11 +1491,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B47,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B47,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B47,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B47,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1510,11 +1510,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B48,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B48,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B48,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B48,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1529,11 +1529,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B49,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B49,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B49,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B49,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1548,11 +1548,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B50,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B50,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B50,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B50,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1567,11 +1567,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B51,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B51,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B51,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B51,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1586,11 +1586,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B52,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B52,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B52,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B52,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1605,11 +1605,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B53,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B53,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B53,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B53,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1624,11 +1624,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B54,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B54,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B54,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B54,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1643,11 +1643,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B55,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B55,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B55,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B55,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1662,11 +1662,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B56,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B56,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B56,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B56,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1681,11 +1681,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B57,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B57,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B57,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B57,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1700,11 +1700,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B58,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B58,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B58,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B58,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1719,11 +1719,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B59,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B59,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B59,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B59,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1738,11 +1738,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B60,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B60,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B60,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B60,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1757,11 +1757,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B61,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B61,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B61,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B61,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1776,11 +1776,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B62,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B62,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B62,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B62,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1795,11 +1795,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B63,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B63,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B63,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B63,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1814,11 +1814,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B64,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B64,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B64,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B64,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1833,11 +1833,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B65,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B65,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B65,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B65,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1852,11 +1852,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B66,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B66,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B66,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B66,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1871,11 +1871,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B67,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B67,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B67,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B67,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1890,11 +1890,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B68,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B68,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B68,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B68,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1909,11 +1909,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B69,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B69,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B69,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B69,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1928,11 +1928,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B70,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B70,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B70,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B70,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1947,11 +1947,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B71,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B71,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B71,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B71,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1966,11 +1966,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B72,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B72,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B72,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B72,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1985,11 +1985,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B73,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B73,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B73,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B73,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2004,11 +2004,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B74,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B74,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B74,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B74,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2023,11 +2023,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B75,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B75,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B75,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B75,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2042,11 +2042,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B76,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B76,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B76,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B76,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2061,11 +2061,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B77,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B77,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B77,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B77,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2080,11 +2080,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B78,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B78,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B78,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B78,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2099,11 +2099,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B79,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B79,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B79,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B79,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2118,11 +2118,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B80,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B80,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B80,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B80,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2137,11 +2137,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B81,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B81,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B81,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B81,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2156,11 +2156,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B82,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B82,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B82,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B82,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2175,11 +2175,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B83,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B83,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B83,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B83,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2194,11 +2194,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B84,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B84,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B84,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B84,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2213,11 +2213,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B85,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B85,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B85,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B85,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2232,11 +2232,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B86,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B86,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B86,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B86,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2251,11 +2251,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B87,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B87,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B87,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B87,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2270,11 +2270,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B88,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B88,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B88,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B88,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2289,11 +2289,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B89,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B89,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B89,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B89,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2308,11 +2308,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B90,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B90,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B90,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B90,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2327,11 +2327,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B91,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B91,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B91,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B91,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2346,11 +2346,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B92,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B92,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B92,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B92,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2365,11 +2365,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B93,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B93,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B93,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B93,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2384,11 +2384,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B94,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B94,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B94,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B94,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2403,11 +2403,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B95,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B95,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B95,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B95,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2422,11 +2422,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B96,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B96,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B96,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B96,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2441,11 +2441,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B97,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B97,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B97,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B97,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2460,11 +2460,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B98,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B98,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B98,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B98,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2479,11 +2479,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B99,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B99,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B99,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B99,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2498,11 +2498,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B100,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B100,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B100,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B100,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2517,11 +2517,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B101,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B101,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B101,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B101,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2536,11 +2536,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B102,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B102,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B102,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B102,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2555,11 +2555,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B103,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B103,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B103,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B103,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2574,11 +2574,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B104,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B104,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B104,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B104,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2593,11 +2593,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B105,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B105,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B105,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B105,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2612,11 +2612,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B106,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B106,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B106,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B106,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2631,11 +2631,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B107,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B107,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B107,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B107,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2650,11 +2650,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B108,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B108,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B108,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B108,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2669,11 +2669,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B109,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B109,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B109,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B109,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2688,11 +2688,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B110,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B110,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B110,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B110,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2707,11 +2707,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B111,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B111,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B111,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B111,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2726,11 +2726,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B112,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B112,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B112,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B112,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2745,11 +2745,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B113,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B113,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B113,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B113,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2764,11 +2764,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B114,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B114,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B114,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B114,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2783,11 +2783,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B115,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B115,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B115,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B115,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2802,11 +2802,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B116,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B116,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B116,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B116,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2821,11 +2821,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B117,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B117,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B117,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B117,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2840,11 +2840,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B118,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B118,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B118,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B118,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2859,11 +2859,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B119,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B119,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B119,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B119,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2878,11 +2878,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B120,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B120,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B120,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B120,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2897,11 +2897,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B121,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B121,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B121,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B121,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2916,11 +2916,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B122,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B122,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B122,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B122,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2935,11 +2935,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B123,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B123,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B123,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B123,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2954,11 +2954,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B124,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B124,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B124,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B124,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2973,11 +2973,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B125,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B125,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B125,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B125,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2992,11 +2992,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B126,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B126,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B126,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B126,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3011,11 +3011,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B127,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B127,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B127,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B127,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3030,11 +3030,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B128,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B128,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B128,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B128,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3049,11 +3049,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B129,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B129,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B129,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B129,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3068,11 +3068,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B130,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B130,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B130,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B130,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3087,11 +3087,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B131,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B131,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B131,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B131,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3106,11 +3106,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B132,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B132,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B132,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B132,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3125,11 +3125,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B133,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B133,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B133,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B133,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3144,11 +3144,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B134,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B134,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B134,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B134,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3163,11 +3163,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B135,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B135,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B135,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B135,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3182,11 +3182,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B136,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B136,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B136,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B136,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3201,11 +3201,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B137,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B137,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B137,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B137,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3220,11 +3220,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B138,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B138,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B138,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B138,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3239,11 +3239,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B139,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B139,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B139,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B139,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3258,11 +3258,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B140,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B140,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B140,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B140,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3277,11 +3277,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B141,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B141,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B141,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B141,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3296,11 +3296,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B142,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B142,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B142,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B142,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3315,11 +3315,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B143,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B143,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B143,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B143,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3334,11 +3334,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B144,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B144,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B144,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B144,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3353,11 +3353,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B145,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B145,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B145,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B145,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3372,11 +3372,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B146,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B146,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B146,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B146,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3391,11 +3391,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B147,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B147,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B147,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B147,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3410,11 +3410,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B148,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B148,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B148,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B148,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3429,11 +3429,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B149,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B149,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B149,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B149,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3448,11 +3448,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B150,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B150,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B150,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B150,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3467,11 +3467,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B151,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B151,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B151,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B151,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3486,11 +3486,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B152,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B152,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B152,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B152,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3505,11 +3505,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B153,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B153,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B153,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B153,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3524,11 +3524,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B154,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B154,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B154,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B154,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3543,11 +3543,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B155,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B155,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B155,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B155,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3562,11 +3562,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B156,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B156,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B156,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B156,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3581,11 +3581,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B157,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B157,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B157,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B157,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3600,11 +3600,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B158,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B158,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B158,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B158,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3619,11 +3619,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B159,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B159,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B159,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B159,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3638,11 +3638,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B160,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B160,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B160,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B160,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3657,11 +3657,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B161,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B161,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B161,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B161,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3676,11 +3676,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B162,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B162,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B162,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B162,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3695,11 +3695,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B163,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B163,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B163,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B163,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3714,11 +3714,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B164,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B164,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B164,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B164,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3733,11 +3733,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B165,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B165,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B165,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B165,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3752,11 +3752,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B166,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B166,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B166,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B166,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3771,11 +3771,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B167,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B167,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B167,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B167,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3790,11 +3790,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B168,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B168,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B168,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B168,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3809,11 +3809,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B169,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B169,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B169,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B169,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3828,11 +3828,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B170,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B170,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B170,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B170,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3847,11 +3847,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B171,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B171,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B171,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B171,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3866,11 +3866,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B172,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B172,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B172,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B172,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3885,11 +3885,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B173,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B173,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B173,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B173,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3904,11 +3904,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B174,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B174,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B174,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B174,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3923,11 +3923,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B175,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B175,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B175,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B175,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3942,11 +3942,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B176,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B176,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B176,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B176,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3961,11 +3961,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B177,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B177,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B177,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B177,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3980,11 +3980,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B178,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B178,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B178,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B178,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3999,11 +3999,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B179,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B179,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B179,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B179,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4018,11 +4018,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B180,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B180,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B180,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B180,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4037,11 +4037,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B181,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B181,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B181,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B181,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4056,11 +4056,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B182,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B182,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B182,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B182,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4075,11 +4075,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B183,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B183,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B183,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B183,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4094,11 +4094,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B184,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B184,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B184,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B184,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4113,11 +4113,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B185,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B185,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B185,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B185,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4132,11 +4132,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B186,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B186,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B186,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B186,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4151,11 +4151,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B187,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B187,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B187,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B187,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4170,11 +4170,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B188,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B188,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B188,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B188,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4189,11 +4189,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B189,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B189,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B189,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B189,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4208,11 +4208,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B190,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B190,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B190,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B190,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4227,11 +4227,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B191,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B191,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B191,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B191,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4246,11 +4246,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B192,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B192,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B192,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B192,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4265,11 +4265,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B193,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B193,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B193,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B193,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4284,11 +4284,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B194,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B194,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B194,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B194,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4303,11 +4303,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B195,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B195,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B195,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B195,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4322,11 +4322,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B196,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B196,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B196,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B196,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4341,11 +4341,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B197,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B197,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B197,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B197,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4360,11 +4360,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B198,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B198,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B198,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B198,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4379,11 +4379,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B199,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B199,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B199,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B199,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4398,11 +4398,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B200,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B200,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B200,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B200,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4417,11 +4417,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B201,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B201,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B201,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B201,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4436,11 +4436,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B202,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B202,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B202,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B202,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4455,11 +4455,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B203,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B203,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B203,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B203,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4474,11 +4474,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B204,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B204,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B204,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B204,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4493,11 +4493,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B205,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B205,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B205,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B205,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4512,11 +4512,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B206,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B206,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B206,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B206,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4531,11 +4531,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B207,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B207,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B207,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B207,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4550,11 +4550,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B208,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B208,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B208,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B208,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4569,11 +4569,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B209,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B209,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B209,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B209,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4588,11 +4588,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B210,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B210,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B210,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B210,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4607,11 +4607,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B211,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B211,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B211,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B211,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4626,11 +4626,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B212,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B212,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B212,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B212,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4645,11 +4645,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B213,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B213,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B213,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B213,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4664,11 +4664,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B214,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B214,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B214,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B214,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4683,11 +4683,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B215,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B215,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B215,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B215,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4702,11 +4702,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B216,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B216,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B216,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B216,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4721,11 +4721,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B217,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B217,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B217,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B217,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4740,11 +4740,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B218,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B218,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B218,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B218,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4759,11 +4759,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B219,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B219,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B219,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B219,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4778,11 +4778,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B220,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B220,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B220,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B220,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4797,11 +4797,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B221,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B221,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B221,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B221,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4816,11 +4816,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B222,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B222,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B222,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B222,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4835,11 +4835,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B223,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B223,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B223,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B223,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4854,11 +4854,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B224,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B224,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B224,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B224,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4873,11 +4873,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B225,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B225,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B225,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B225,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4892,11 +4892,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B226,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B226,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B226,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B226,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4911,11 +4911,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B227,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B227,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B227,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B227,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4930,11 +4930,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B228,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B228,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B228,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B228,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4949,11 +4949,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B229,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B229,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B229,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B229,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4968,11 +4968,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B230,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B230,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B230,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B230,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4987,11 +4987,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B231,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B231,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B231,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B231,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5006,11 +5006,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B232,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B232,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B232,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B232,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5025,11 +5025,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B233,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B233,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B233,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B233,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5044,11 +5044,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B234,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B234,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B234,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B234,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5063,11 +5063,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B235,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B235,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B235,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B235,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5082,11 +5082,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B236,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B236,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B236,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B236,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5101,11 +5101,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B237,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B237,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B237,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B237,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5120,11 +5120,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B238,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B238,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B238,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B238,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5139,11 +5139,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B239,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B239,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B239,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B239,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5158,11 +5158,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B240,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B240,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B240,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B240,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5177,11 +5177,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B241,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B241,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B241,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B241,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5196,11 +5196,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B242,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B242,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B242,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B242,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5215,11 +5215,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B243,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B243,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B243,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B243,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5234,11 +5234,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B244,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B244,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B244,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B244,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5253,11 +5253,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B245,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B245,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B245,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B245,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5272,11 +5272,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B246,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B246,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B246,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B246,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5291,11 +5291,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B247,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B247,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B247,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B247,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5310,11 +5310,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B248,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B248,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B248,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B248,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5329,11 +5329,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B249,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B249,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B249,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B249,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5348,11 +5348,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B250,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B250,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B250,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B250,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5367,11 +5367,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B251,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B251,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B251,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B251,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5386,11 +5386,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B252,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B252,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B252,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B252,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5405,11 +5405,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B253,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B253,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B253,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B253,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5424,11 +5424,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B254,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B254,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B254,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B254,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5443,11 +5443,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B255,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B255,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B255,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B255,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5462,11 +5462,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B256,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B256,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B256,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B256,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5481,11 +5481,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B257,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B257,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B257,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B257,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5500,11 +5500,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B258,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B258,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B258,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B258,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5519,11 +5519,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B259,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B259,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B259,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B259,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5538,11 +5538,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B260,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B260,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B260,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B260,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5557,11 +5557,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B261,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B261,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B261,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B261,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5576,11 +5576,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B262,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B262,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B262,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B262,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5595,11 +5595,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B263,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B263,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B263,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B263,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5614,11 +5614,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B264,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B264,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B264,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B264,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5633,11 +5633,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B265,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B265,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B265,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B265,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5652,11 +5652,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B266,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B266,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B266,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B266,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5671,11 +5671,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B267,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B267,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B267,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B267,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5690,11 +5690,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B268,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B268,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B268,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B268,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5709,11 +5709,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B269,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B269,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B269,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B269,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5728,11 +5728,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B270,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B270,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B270,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B270,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5747,11 +5747,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B271,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B271,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B271,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B271,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5766,11 +5766,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B272,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B272,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B272,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B272,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5785,11 +5785,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B273,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B273,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B273,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B273,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5804,11 +5804,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B274,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B274,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B274,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B274,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5823,11 +5823,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B275,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B275,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B275,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B275,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5842,11 +5842,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B276,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B276,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B276,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B276,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5861,11 +5861,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B277,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B277,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B277,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B277,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5880,11 +5880,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B278,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B278,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B278,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B278,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5899,11 +5899,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B279,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B279,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B279,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B279,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5918,11 +5918,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B280,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B280,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B280,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B280,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5937,11 +5937,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B281,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B281,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B281,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B281,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5956,11 +5956,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B282,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B282,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B282,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B282,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5975,11 +5975,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B283,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B283,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B283,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B283,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5994,11 +5994,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B284,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B284,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B284,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B284,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6013,11 +6013,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B285,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B285,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B285,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B285,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6032,11 +6032,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B286,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B286,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B286,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B286,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6051,11 +6051,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B287,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B287,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B287,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B287,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6070,11 +6070,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B288,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B288,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B288,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B288,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6089,11 +6089,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B289,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B289,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B289,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B289,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6108,11 +6108,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B290,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B290,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B290,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B290,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6127,11 +6127,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B291,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B291,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B291,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B291,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6146,11 +6146,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B292,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B292,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B292,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B292,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6165,11 +6165,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B293,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B293,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B293,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B293,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6184,11 +6184,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B294,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B294,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B294,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B294,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6203,11 +6203,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B295,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B295,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B295,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B295,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6222,11 +6222,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B296,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B296,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B296,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B296,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6241,11 +6241,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B297,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B297,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B297,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B297,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6260,11 +6260,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B298,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B298,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B298,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B298,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6279,11 +6279,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B299,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B299,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B299,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B299,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6298,11 +6298,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B300,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B300,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B300,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B300,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6317,11 +6317,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B301,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B301,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B301,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B301,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6336,11 +6336,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B302,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B302,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B302,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B302,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6355,11 +6355,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B303,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B303,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B303,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B303,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6374,11 +6374,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B304,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B304,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B304,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B304,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6393,11 +6393,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B305,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B305,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B305,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B305,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6412,11 +6412,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B306,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B306,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B306,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B306,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6431,11 +6431,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B307,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B307,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B307,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B307,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6450,11 +6450,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B308,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B308,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B308,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B308,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6469,11 +6469,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B309,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B309,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B309,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B309,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6488,11 +6488,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B310,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B310,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B310,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B310,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6507,11 +6507,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B311,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B311,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B311,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B311,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6526,11 +6526,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B312,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B312,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B312,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B312,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6545,11 +6545,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B313,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B313,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B313,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B313,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6564,11 +6564,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B314,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B314,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B314,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B314,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6583,11 +6583,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B315,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B315,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B315,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B315,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6602,11 +6602,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B316,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B316,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B316,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B316,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6621,11 +6621,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B317,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B317,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B317,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B317,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6640,11 +6640,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B318,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B318,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B318,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B318,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6659,11 +6659,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B319,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B319,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B319,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B319,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6678,11 +6678,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B320,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B320,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B320,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B320,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6697,11 +6697,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B321,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B321,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B321,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B321,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6716,11 +6716,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B322,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B322,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B322,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B322,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6735,11 +6735,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B323,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B323,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B323,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B323,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6754,11 +6754,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B324,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B324,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B324,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B324,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6773,11 +6773,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B325,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B325,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B325,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B325,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6792,11 +6792,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B326,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B326,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B326,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B326,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6811,11 +6811,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B327,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B327,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B327,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B327,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6830,11 +6830,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B328,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B328,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B328,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B328,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6849,11 +6849,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B329,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B329,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B329,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B329,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6868,11 +6868,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B330,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B330,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B330,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B330,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6887,11 +6887,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B331,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B331,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B331,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B331,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6906,11 +6906,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B332,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B332,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B332,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B332,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6925,11 +6925,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B333,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B333,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B333,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B333,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6944,11 +6944,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B334,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B334,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B334,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B334,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6963,11 +6963,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B335,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B335,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B335,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B335,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6982,11 +6982,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B336,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B336,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B336,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B336,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7001,11 +7001,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B337,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B337,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B337,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B337,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7020,11 +7020,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B338,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B338,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B338,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B338,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7039,11 +7039,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B339,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B339,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B339,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B339,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7058,11 +7058,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B340,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B340,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B340,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B340,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7077,11 +7077,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B341,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B341,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B341,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B341,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7096,11 +7096,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B342,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B342,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B342,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B342,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7115,11 +7115,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B343,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B343,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B343,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B343,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7134,11 +7134,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B344,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B344,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B344,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B344,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7153,11 +7153,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B345,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B345,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B345,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B345,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7172,11 +7172,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B346,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B346,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B346,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B346,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7191,11 +7191,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B347,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B347,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B347,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B347,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7210,11 +7210,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B348,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B348,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B348,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B348,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7229,11 +7229,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B349,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B349,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B349,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B349,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7248,11 +7248,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B350,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B350,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B350,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B350,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7267,11 +7267,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B351,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B351,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B351,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B351,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7286,11 +7286,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B352,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B352,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B352,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B352,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7305,11 +7305,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B353,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B353,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B353,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B353,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7324,11 +7324,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B354,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B354,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B354,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B354,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7343,11 +7343,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B355,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B355,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B355,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B355,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7362,11 +7362,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B356,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B356,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B356,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B356,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7381,11 +7381,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B357,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B357,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B357,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B357,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7400,11 +7400,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B358,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B358,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B358,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B358,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7419,11 +7419,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B359,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B359,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B359,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B359,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7438,11 +7438,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B360,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B360,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B360,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B360,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7457,11 +7457,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B361,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B361,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B361,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B361,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7476,11 +7476,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B362,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B362,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B362,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B362,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7495,11 +7495,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B363,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B363,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B363,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B363,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7514,11 +7514,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B364,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B364,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B364,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B364,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7533,11 +7533,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B365,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B365,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B365,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B365,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7552,11 +7552,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B366,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B366,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B366,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B366,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7571,11 +7571,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B367,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B367,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B367,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B367,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7590,11 +7590,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B368,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B368,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B368,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B368,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7609,11 +7609,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B369,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B369,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B369,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B369,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7628,11 +7628,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B370,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B370,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B370,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B370,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7647,11 +7647,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B371,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B371,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B371,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B371,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7666,11 +7666,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B372,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B372,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B372,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B372,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7685,11 +7685,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B373,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B373,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B373,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B373,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7704,11 +7704,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B374,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B374,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B374,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B374,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7723,11 +7723,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B375,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B375,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B375,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B375,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7742,11 +7742,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B376,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B376,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B376,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B376,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7761,11 +7761,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B377,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B377,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B377,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B377,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7780,11 +7780,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B378,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B378,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B378,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B378,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7799,11 +7799,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B379,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B379,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B379,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B379,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7818,11 +7818,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B380,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B380,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B380,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B380,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7837,11 +7837,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B381,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B381,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B381,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B381,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7856,11 +7856,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B382,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B382,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B382,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B382,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7875,11 +7875,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B383,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B383,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B383,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B383,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7894,11 +7894,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B384,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B384,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B384,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B384,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7913,11 +7913,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B385,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B385,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B385,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B385,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7932,11 +7932,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B386,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B386,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B386,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B386,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7951,11 +7951,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B387,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B387,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B387,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B387,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7970,11 +7970,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B388,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B388,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B388,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B388,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7989,11 +7989,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B389,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B389,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B389,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B389,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8008,11 +8008,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B390,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B390,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B390,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B390,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8027,11 +8027,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B391,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B391,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B391,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B391,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8046,11 +8046,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B392,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B392,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B392,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B392,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8065,11 +8065,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B393,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B393,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B393,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B393,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8084,11 +8084,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B394,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B394,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B394,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B394,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8103,11 +8103,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B395,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B395,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B395,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B395,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8122,11 +8122,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B396,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B396,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B396,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B396,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8141,11 +8141,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B397,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B397,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B397,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B397,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8160,11 +8160,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B398,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B398,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B398,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B398,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8179,11 +8179,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B399,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B399,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B399,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B399,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8198,11 +8198,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B400,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B400,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B400,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B400,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8217,11 +8217,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B401,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B401,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B401,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B401,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8236,11 +8236,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$76,MATCH(B402,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$75,MATCH(B402,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$76,MATCH(B402,Productos!$A$2:$A$76,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$75,MATCH(B402,Productos!$A$2:$A$75,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -8769,11 +8769,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -9077,7 +9072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9434,7 +9429,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9454,7 +9449,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9474,7 +9469,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9585,12 +9580,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -9605,16 +9600,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9625,16 +9620,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90400340000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9645,16 +9640,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90400340000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9665,36 +9660,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>90322670000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9705,16 +9700,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90322670000</t>
+          <t>90322650000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -9725,16 +9720,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90322650000</t>
+          <t>90301720000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9745,36 +9740,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -9785,16 +9780,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9805,16 +9800,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9825,16 +9820,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9845,16 +9840,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9865,16 +9860,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -9885,16 +9880,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9905,16 +9900,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90410970000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9925,16 +9920,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -9945,16 +9940,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -9965,36 +9960,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>OLA COBAYOS 800GRS. · 90405610000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90405610000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OLA COBAYOS 800GRS. · 90405610000</t>
+          <t>OLA CONEJOS 800GRS · 90405620000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90405610000</t>
+          <t>90405620000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -10005,16 +10000,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OLA CONEJOS 800GRS · 90405620000</t>
+          <t>OLA HAMSTERS 800GRS · 90405600000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90405620000</t>
+          <t>90405600000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10025,36 +10020,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OLA HAMSTERS 800GRS · 90405600000</t>
+          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90405600000</t>
+          <t>93509400000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
+          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93509400000</t>
+          <t>93509410000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10065,16 +10060,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
+          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93509410000</t>
+          <t>93512280000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10085,52 +10080,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93512280000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D WS POLLO Y ARROZ INTEGRAL 30L · 93500000230</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93500000230</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUNSHINE MILLS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D WS POLLO Y ARROZ INTEGRAL 30L · 93500000230</t>
+          <t>D SK ALIM LATA POLLO 400GR · 93511650000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93500000230</t>
+          <t>93511650000</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -10138,23 +10133,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SUNSHINE MILLS</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA POLLO 400GR · 93511650000</t>
+          <t>D SK ALIM LATA POLLO/RES/TOCINO 400GR · 93511660000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93511650000</t>
+          <t>93511660000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10165,16 +10160,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA POLLO/RES/TOCINO 400GR · 93511660000</t>
+          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93511660000</t>
+          <t>93511640000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10185,16 +10180,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
+          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93511640000</t>
+          <t>93511680000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10205,16 +10200,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>93511680000</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10225,16 +10220,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10245,16 +10240,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ADULTOS 4KG · 93500000343</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93500000343</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10265,16 +10260,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 4KG · 93500000343</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>93500000343</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10285,16 +10280,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10305,36 +10300,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>D SUPRA ALIM LATA TROZOS D CARNE 14OZ · 93509270000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93509270000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D SUPRA ALIM LATA TROZOS D CARNE 14OZ · 93509270000</t>
+          <t>D SUPRA ALIM LATA TROZOS D POLLO 14OZ · 93509280000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>93509270000</t>
+          <t>93509280000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10345,16 +10340,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D SUPRA ALIM LATA TROZOS D POLLO 14OZ · 93509280000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>93509280000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10365,16 +10360,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10385,16 +10380,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10405,16 +10400,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10425,16 +10420,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10445,16 +10440,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508950000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10465,16 +10460,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>93508950000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10485,56 +10480,56 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90409060000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90409060000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10545,16 +10540,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90409050000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10565,74 +10560,54 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90409070000</t>
+          <t>93503060000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>93503060000</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>4</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
           <t>ZOO MED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MELO &amp; CIA. | LA VILLA</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MELO &amp; CIA. | LA VILLA</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/38.xlsx
+++ b/plantillas/38.xlsx
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
